--- a/scanlag_data/CASP+SHX/casp+shx.xlsx
+++ b/scanlag_data/CASP+SHX/casp+shx.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/along/Documents/Projects/manuscript_reviews/scanlag_data/CASP+SHX/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Documents\Projects\manuscript_reviews\scanlag_data\CASP+SHX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED5201A-1499-AB42-90EC-AC6DBA9342A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5724D399-FB33-48EB-8428-9C62C3665950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19580" xr2:uid="{D4D66D7A-7CBE-F841-B5C8-F2727FA1750C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4D66D7A-7CBE-F841-B5C8-F2727FA1750C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,12 +53,6 @@
     <t>Tw=1315_minutes</t>
   </si>
   <si>
-    <t>t0=-48</t>
-  </si>
-  <si>
-    <t>t0=-62</t>
-  </si>
-  <si>
     <t>Dis-Arrest</t>
   </si>
   <si>
@@ -71,7 +65,13 @@
     <t>Reg-Arrest</t>
   </si>
   <si>
-    <t>t0=-74.5</t>
+    <t>t0=0</t>
+  </si>
+  <si>
+    <t>t0=72</t>
+  </si>
+  <si>
+    <t>t0=74</t>
   </si>
 </sst>
 </file>
@@ -444,29 +444,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171D98BA-8D96-2B45-A1AF-DF69EF76EE41}">
-  <dimension ref="A1:F485"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H485"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="16.625" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,21 +474,21 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -508,7 +508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>-13</v>
       </c>
@@ -528,7 +528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0</v>
       </c>
@@ -547,8 +547,9 @@
       <c r="F6">
         <v>0.99789473684210528</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -567,8 +568,9 @@
       <c r="F7">
         <v>0.99578947368421056</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>30</v>
       </c>
@@ -587,8 +589,9 @@
       <c r="F8">
         <v>0.99368421052631584</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>31</v>
       </c>
@@ -608,7 +611,7 @@
         <v>0.991578947368421</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>31</v>
       </c>
@@ -628,7 +631,7 @@
         <v>0.98947368421052628</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>31</v>
       </c>
@@ -648,7 +651,7 @@
         <v>0.98736842105263156</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>32</v>
       </c>
@@ -668,7 +671,7 @@
         <v>0.98526315789473684</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>32</v>
       </c>
@@ -688,7 +691,7 @@
         <v>0.98315789473684212</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>32</v>
       </c>
@@ -708,7 +711,7 @@
         <v>0.9810526315789474</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>33</v>
       </c>
@@ -728,7 +731,7 @@
         <v>0.97894736842105268</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>45</v>
       </c>
@@ -748,7 +751,7 @@
         <v>0.97684210526315784</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>45</v>
       </c>
@@ -768,7 +771,7 @@
         <v>0.97473684210526312</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>46</v>
       </c>
@@ -788,7 +791,7 @@
         <v>0.9726315789473684</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>46</v>
       </c>
@@ -808,7 +811,7 @@
         <v>0.97052631578947368</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>46</v>
       </c>
@@ -828,7 +831,7 @@
         <v>0.96842105263157896</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>46</v>
       </c>
@@ -848,7 +851,7 @@
         <v>0.96631578947368424</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>46</v>
       </c>
@@ -868,7 +871,7 @@
         <v>0.96421052631578952</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>46</v>
       </c>
@@ -888,7 +891,7 @@
         <v>0.96210526315789469</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>46</v>
       </c>
@@ -908,7 +911,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>46</v>
       </c>
@@ -928,7 +931,7 @@
         <v>0.95789473684210524</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>47</v>
       </c>
@@ -948,7 +951,7 @@
         <v>0.95578947368421052</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>47</v>
       </c>
@@ -968,7 +971,7 @@
         <v>0.9536842105263158</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>47</v>
       </c>
@@ -988,7 +991,7 @@
         <v>0.95157894736842108</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>47</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>0.94947368421052636</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>47</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>0.94736842105263153</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>47</v>
       </c>
@@ -1048,7 +1051,7 @@
         <v>0.94526315789473681</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>47</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>0.94315789473684208</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>47</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>0.94105263157894736</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>47</v>
       </c>
@@ -1108,7 +1111,7 @@
         <v>0.93894736842105264</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>47</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>0.93684210526315792</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>48</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>0.9347368421052632</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>48</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>0.93263157894736837</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>60</v>
       </c>
@@ -1188,7 +1191,7 @@
         <v>0.93052631578947365</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>60</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>0.92842105263157892</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>60</v>
       </c>
@@ -1228,7 +1231,7 @@
         <v>0.9263157894736842</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>61</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>0.92421052631578948</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>61</v>
       </c>
@@ -1268,7 +1271,7 @@
         <v>0.92210526315789476</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>61</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>61</v>
       </c>
@@ -1308,7 +1311,7 @@
         <v>0.91789473684210521</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>61</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>0.91578947368421049</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>61</v>
       </c>
@@ -1348,7 +1351,7 @@
         <v>0.91368421052631577</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>61</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>0.91157894736842104</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>61</v>
       </c>
@@ -1388,7 +1391,7 @@
         <v>0.90947368421052632</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>61</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>0.9073684210526316</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>61</v>
       </c>
@@ -1428,7 +1431,7 @@
         <v>0.90526315789473688</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>62</v>
       </c>
@@ -1448,7 +1451,7 @@
         <v>0.90315789473684216</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>62</v>
       </c>
@@ -1468,7 +1471,7 @@
         <v>0.90105263157894733</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>62</v>
       </c>
@@ -1488,7 +1491,7 @@
         <v>0.89894736842105261</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>62</v>
       </c>
@@ -1508,7 +1511,7 @@
         <v>0.89684210526315788</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>62</v>
       </c>
@@ -1528,7 +1531,7 @@
         <v>0.89473684210526316</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>62</v>
       </c>
@@ -1548,7 +1551,7 @@
         <v>0.89263157894736844</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>62</v>
       </c>
@@ -1568,7 +1571,7 @@
         <v>0.89052631578947372</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>62</v>
       </c>
@@ -1588,7 +1591,7 @@
         <v>0.888421052631579</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>0.88631578947368417</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>62</v>
       </c>
@@ -1628,7 +1631,7 @@
         <v>0.88421052631578945</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>62</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>0.88210526315789473</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>62</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>63</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>0.87789473684210528</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>0.87578947368421056</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1728,7 +1731,7 @@
         <v>0.87368421052631584</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>63</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>0.87157894736842101</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>75</v>
       </c>
@@ -1768,7 +1771,7 @@
         <v>0.86947368421052629</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>75</v>
       </c>
@@ -1788,7 +1791,7 @@
         <v>0.86736842105263157</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>75</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>0.86526315789473685</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>75</v>
       </c>
@@ -1828,7 +1831,7 @@
         <v>0.86315789473684212</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>75</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>0.8610526315789474</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>0.85894736842105268</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>75</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>0.85684210526315785</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>75</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>0.85473684210526313</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>75</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>0.85263157894736841</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1948,7 +1951,7 @@
         <v>0.85052631578947369</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1968,7 +1971,7 @@
         <v>0.84842105263157896</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>75</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>0.84631578947368424</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>75</v>
       </c>
@@ -2008,7 +2011,7 @@
         <v>0.84421052631578952</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>76</v>
       </c>
@@ -2028,7 +2031,7 @@
         <v>0.84210526315789469</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>76</v>
       </c>
@@ -2048,7 +2051,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>76</v>
       </c>
@@ -2068,7 +2071,7 @@
         <v>0.83789473684210525</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>76</v>
       </c>
@@ -2088,7 +2091,7 @@
         <v>0.83578947368421053</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>76</v>
       </c>
@@ -2108,7 +2111,7 @@
         <v>0.83368421052631581</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>76</v>
       </c>
@@ -2128,7 +2131,7 @@
         <v>0.83157894736842108</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>76</v>
       </c>
@@ -2148,7 +2151,7 @@
         <v>0.82947368421052636</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>76</v>
       </c>
@@ -2168,7 +2171,7 @@
         <v>0.82736842105263153</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>77</v>
       </c>
@@ -2188,7 +2191,7 @@
         <v>0.82526315789473681</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>77</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>0.82315789473684209</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>77</v>
       </c>
@@ -2228,7 +2231,7 @@
         <v>0.82105263157894737</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>77</v>
       </c>
@@ -2248,7 +2251,7 @@
         <v>0.81894736842105265</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>77</v>
       </c>
@@ -2268,7 +2271,7 @@
         <v>0.81684210526315792</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>77</v>
       </c>
@@ -2288,7 +2291,7 @@
         <v>0.8147368421052632</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>77</v>
       </c>
@@ -2308,7 +2311,7 @@
         <v>0.81263157894736837</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>77</v>
       </c>
@@ -2328,7 +2331,7 @@
         <v>0.81052631578947365</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>77</v>
       </c>
@@ -2348,7 +2351,7 @@
         <v>0.80842105263157893</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>77</v>
       </c>
@@ -2368,7 +2371,7 @@
         <v>0.80631578947368421</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>77</v>
       </c>
@@ -2388,7 +2391,7 @@
         <v>0.80421052631578949</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>77</v>
       </c>
@@ -2408,7 +2411,7 @@
         <v>0.80210526315789477</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>77</v>
       </c>
@@ -2428,7 +2431,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>77</v>
       </c>
@@ -2448,7 +2451,7 @@
         <v>0.79789473684210521</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>77</v>
       </c>
@@ -2468,7 +2471,7 @@
         <v>0.79578947368421049</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>77</v>
       </c>
@@ -2488,7 +2491,7 @@
         <v>0.79368421052631577</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>77</v>
       </c>
@@ -2508,7 +2511,7 @@
         <v>0.79157894736842105</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>77</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>0.78947368421052633</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>77</v>
       </c>
@@ -2548,7 +2551,7 @@
         <v>0.78736842105263161</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>77</v>
       </c>
@@ -2568,7 +2571,7 @@
         <v>0.78526315789473689</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>77</v>
       </c>
@@ -2588,7 +2591,7 @@
         <v>0.78315789473684205</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>77</v>
       </c>
@@ -2608,7 +2611,7 @@
         <v>0.78105263157894733</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>77</v>
       </c>
@@ -2628,7 +2631,7 @@
         <v>0.77894736842105261</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>77</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>0.77684210526315789</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>77</v>
       </c>
@@ -2668,7 +2671,7 @@
         <v>0.77473684210526317</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>78</v>
       </c>
@@ -2688,7 +2691,7 @@
         <v>0.77263157894736845</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>78</v>
       </c>
@@ -2708,7 +2711,7 @@
         <v>0.77052631578947373</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>78</v>
       </c>
@@ -2728,7 +2731,7 @@
         <v>0.76842105263157889</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>78</v>
       </c>
@@ -2748,7 +2751,7 @@
         <v>0.76631578947368417</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>78</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>0.76421052631578945</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>78</v>
       </c>
@@ -2788,7 +2791,7 @@
         <v>0.76210526315789473</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>78</v>
       </c>
@@ -2808,7 +2811,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>78</v>
       </c>
@@ -2828,7 +2831,7 @@
         <v>0.75789473684210529</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>90</v>
       </c>
@@ -2848,7 +2851,7 @@
         <v>0.75578947368421057</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>90</v>
       </c>
@@ -2868,7 +2871,7 @@
         <v>0.75368421052631573</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>90</v>
       </c>
@@ -2888,7 +2891,7 @@
         <v>0.75157894736842101</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>90</v>
       </c>
@@ -2908,7 +2911,7 @@
         <v>0.74947368421052629</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>90</v>
       </c>
@@ -2928,7 +2931,7 @@
         <v>0.74736842105263157</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>90</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>0.74526315789473685</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>90</v>
       </c>
@@ -2968,7 +2971,7 @@
         <v>0.74315789473684213</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>90</v>
       </c>
@@ -2988,7 +2991,7 @@
         <v>0.74105263157894741</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>90</v>
       </c>
@@ -3008,7 +3011,7 @@
         <v>0.73894736842105269</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>90</v>
       </c>
@@ -3028,7 +3031,7 @@
         <v>0.73684210526315785</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>90</v>
       </c>
@@ -3048,7 +3051,7 @@
         <v>0.73473684210526313</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>90</v>
       </c>
@@ -3068,7 +3071,7 @@
         <v>0.73263157894736841</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>90</v>
       </c>
@@ -3088,7 +3091,7 @@
         <v>0.73052631578947369</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>90</v>
       </c>
@@ -3108,7 +3111,7 @@
         <v>0.72842105263157897</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>90</v>
       </c>
@@ -3128,7 +3131,7 @@
         <v>0.72631578947368425</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>90</v>
       </c>
@@ -3148,7 +3151,7 @@
         <v>0.72421052631578953</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>90</v>
       </c>
@@ -3168,7 +3171,7 @@
         <v>0.72210526315789469</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>90</v>
       </c>
@@ -3188,7 +3191,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>91</v>
       </c>
@@ -3208,7 +3211,7 @@
         <v>0.71789473684210525</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>91</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>0.71578947368421053</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>91</v>
       </c>
@@ -3248,7 +3251,7 @@
         <v>0.71368421052631581</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>91</v>
       </c>
@@ -3268,7 +3271,7 @@
         <v>0.71157894736842109</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>91</v>
       </c>
@@ -3288,7 +3291,7 @@
         <v>0.70947368421052637</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>91</v>
       </c>
@@ -3308,7 +3311,7 @@
         <v>0.70736842105263154</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>91</v>
       </c>
@@ -3328,7 +3331,7 @@
         <v>0.70526315789473681</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>91</v>
       </c>
@@ -3348,7 +3351,7 @@
         <v>0.70315789473684209</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>91</v>
       </c>
@@ -3368,7 +3371,7 @@
         <v>0.70105263157894737</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>91</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>0.69894736842105265</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>92</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>0.69684210526315793</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>92</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>0.69473684210526321</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>92</v>
       </c>
@@ -3448,7 +3451,7 @@
         <v>0.69263157894736838</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>92</v>
       </c>
@@ -3468,7 +3471,7 @@
         <v>0.69052631578947365</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>92</v>
       </c>
@@ -3488,7 +3491,7 @@
         <v>0.68842105263157893</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>92</v>
       </c>
@@ -3508,7 +3511,7 @@
         <v>0.68631578947368421</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>92</v>
       </c>
@@ -3528,7 +3531,7 @@
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>92</v>
       </c>
@@ -3548,7 +3551,7 @@
         <v>0.68210526315789477</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>92</v>
       </c>
@@ -3568,7 +3571,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>92</v>
       </c>
@@ -3588,7 +3591,7 @@
         <v>0.67789473684210522</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>92</v>
       </c>
@@ -3608,7 +3611,7 @@
         <v>0.6757894736842105</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>92</v>
       </c>
@@ -3628,7 +3631,7 @@
         <v>0.67368421052631577</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>92</v>
       </c>
@@ -3648,7 +3651,7 @@
         <v>0.67157894736842105</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>92</v>
       </c>
@@ -3668,7 +3671,7 @@
         <v>0.66947368421052633</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>92</v>
       </c>
@@ -3688,7 +3691,7 @@
         <v>0.66736842105263161</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>92</v>
       </c>
@@ -3708,7 +3711,7 @@
         <v>0.66526315789473689</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>92</v>
       </c>
@@ -3728,7 +3731,7 @@
         <v>0.66315789473684206</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>92</v>
       </c>
@@ -3748,7 +3751,7 @@
         <v>0.66105263157894734</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>92</v>
       </c>
@@ -3768,7 +3771,7 @@
         <v>0.65894736842105261</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>92</v>
       </c>
@@ -3788,7 +3791,7 @@
         <v>0.65684210526315789</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>92</v>
       </c>
@@ -3808,7 +3811,7 @@
         <v>0.65473684210526317</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>92</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>0.65263157894736845</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>92</v>
       </c>
@@ -3848,7 +3851,7 @@
         <v>0.65052631578947373</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>92</v>
       </c>
@@ -3868,7 +3871,7 @@
         <v>0.6484210526315789</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>92</v>
       </c>
@@ -3888,7 +3891,7 @@
         <v>0.64631578947368418</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>92</v>
       </c>
@@ -3908,7 +3911,7 @@
         <v>0.64421052631578946</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>92</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>0.64210526315789473</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>92</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>92</v>
       </c>
@@ -3968,7 +3971,7 @@
         <v>0.63789473684210529</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>92</v>
       </c>
@@ -3988,7 +3991,7 @@
         <v>0.63578947368421057</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>92</v>
       </c>
@@ -4008,7 +4011,7 @@
         <v>0.63368421052631574</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>92</v>
       </c>
@@ -4028,7 +4031,7 @@
         <v>0.63157894736842102</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>92</v>
       </c>
@@ -4048,7 +4051,7 @@
         <v>0.6294736842105263</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>93</v>
       </c>
@@ -4068,7 +4071,7 @@
         <v>0.62736842105263158</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>93</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>0.62526315789473685</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>93</v>
       </c>
@@ -4108,7 +4111,7 @@
         <v>0.62315789473684213</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>93</v>
       </c>
@@ -4128,7 +4131,7 @@
         <v>0.62105263157894741</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>93</v>
       </c>
@@ -4148,7 +4151,7 @@
         <v>0.61894736842105258</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>93</v>
       </c>
@@ -4168,7 +4171,7 @@
         <v>0.61684210526315786</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>93</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>0.61473684210526314</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>93</v>
       </c>
@@ -4208,7 +4211,7 @@
         <v>0.61263157894736842</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>93</v>
       </c>
@@ -4228,7 +4231,7 @@
         <v>0.61052631578947369</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>93</v>
       </c>
@@ -4248,7 +4251,7 @@
         <v>0.60842105263157897</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>93</v>
       </c>
@@ -4268,7 +4271,7 @@
         <v>0.60631578947368425</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>93</v>
       </c>
@@ -4288,7 +4291,7 @@
         <v>0.60421052631578942</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>93</v>
       </c>
@@ -4308,7 +4311,7 @@
         <v>0.6021052631578947</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>93</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>93</v>
       </c>
@@ -4348,7 +4351,7 @@
         <v>0.59789473684210526</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>93</v>
       </c>
@@ -4368,7 +4371,7 @@
         <v>0.59578947368421054</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>105</v>
       </c>
@@ -4388,7 +4391,7 @@
         <v>0.59368421052631581</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>105</v>
       </c>
@@ -4408,7 +4411,7 @@
         <v>0.59157894736842109</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>105</v>
       </c>
@@ -4428,7 +4431,7 @@
         <v>0.58947368421052626</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>105</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>0.58736842105263154</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>105</v>
       </c>
@@ -4468,7 +4471,7 @@
         <v>0.58526315789473682</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>105</v>
       </c>
@@ -4488,7 +4491,7 @@
         <v>0.5831578947368421</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>105</v>
       </c>
@@ -4508,7 +4511,7 @@
         <v>0.58105263157894738</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>105</v>
       </c>
@@ -4528,7 +4531,7 @@
         <v>0.57894736842105265</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>105</v>
       </c>
@@ -4548,7 +4551,7 @@
         <v>0.57684210526315793</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>105</v>
       </c>
@@ -4568,7 +4571,7 @@
         <v>0.57473684210526321</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>105</v>
       </c>
@@ -4588,7 +4591,7 @@
         <v>0.57263157894736838</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>105</v>
       </c>
@@ -4608,7 +4611,7 @@
         <v>0.57052631578947366</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>105</v>
       </c>
@@ -4628,7 +4631,7 @@
         <v>0.56842105263157894</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>105</v>
       </c>
@@ -4648,7 +4651,7 @@
         <v>0.56631578947368422</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>105</v>
       </c>
@@ -4668,7 +4671,7 @@
         <v>0.5642105263157895</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>105</v>
       </c>
@@ -4688,7 +4691,7 @@
         <v>0.56210526315789477</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>106</v>
       </c>
@@ -4708,7 +4711,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>106</v>
       </c>
@@ -4728,7 +4731,7 @@
         <v>0.55789473684210522</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>106</v>
       </c>
@@ -4748,7 +4751,7 @@
         <v>0.5557894736842105</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>106</v>
       </c>
@@ -4768,7 +4771,7 @@
         <v>0.55368421052631578</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>106</v>
       </c>
@@ -4788,7 +4791,7 @@
         <v>0.55157894736842106</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>106</v>
       </c>
@@ -4808,7 +4811,7 @@
         <v>0.54947368421052634</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>106</v>
       </c>
@@ -4828,7 +4831,7 @@
         <v>0.54736842105263162</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>107</v>
       </c>
@@ -4848,7 +4851,7 @@
         <v>0.54526315789473689</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>107</v>
       </c>
@@ -4868,7 +4871,7 @@
         <v>0.54315789473684206</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>107</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>0.54105263157894734</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>107</v>
       </c>
@@ -4908,7 +4911,7 @@
         <v>0.53894736842105262</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>107</v>
       </c>
@@ -4928,7 +4931,7 @@
         <v>0.5368421052631579</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>107</v>
       </c>
@@ -4948,7 +4951,7 @@
         <v>0.53473684210526318</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>107</v>
       </c>
@@ -4968,7 +4971,7 @@
         <v>0.53263157894736846</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>107</v>
       </c>
@@ -4988,7 +4991,7 @@
         <v>0.53052631578947373</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>107</v>
       </c>
@@ -5008,7 +5011,7 @@
         <v>0.5284210526315789</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>107</v>
       </c>
@@ -5028,7 +5031,7 @@
         <v>0.52631578947368418</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>107</v>
       </c>
@@ -5048,7 +5051,7 @@
         <v>0.52421052631578946</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>107</v>
       </c>
@@ -5068,7 +5071,7 @@
         <v>0.52210526315789474</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>107</v>
       </c>
@@ -5088,7 +5091,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>107</v>
       </c>
@@ -5108,7 +5111,7 @@
         <v>0.5178947368421053</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>107</v>
       </c>
@@ -5128,7 +5131,7 @@
         <v>0.51578947368421058</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>107</v>
       </c>
@@ -5148,7 +5151,7 @@
         <v>0.51368421052631574</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>107</v>
       </c>
@@ -5168,7 +5171,7 @@
         <v>0.51157894736842102</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>107</v>
       </c>
@@ -5188,7 +5191,7 @@
         <v>0.5094736842105263</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>107</v>
       </c>
@@ -5208,7 +5211,7 @@
         <v>0.50736842105263158</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>107</v>
       </c>
@@ -5228,7 +5231,7 @@
         <v>0.50526315789473686</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>107</v>
       </c>
@@ -5248,7 +5251,7 @@
         <v>0.50315789473684214</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>107</v>
       </c>
@@ -5268,7 +5271,7 @@
         <v>0.50105263157894742</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>107</v>
       </c>
@@ -5288,7 +5291,7 @@
         <v>0.49894736842105264</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>107</v>
       </c>
@@ -5308,7 +5311,7 @@
         <v>0.49684210526315792</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>107</v>
       </c>
@@ -5328,7 +5331,7 @@
         <v>0.49473684210526314</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>107</v>
       </c>
@@ -5348,7 +5351,7 @@
         <v>0.49263157894736842</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>107</v>
       </c>
@@ -5368,7 +5371,7 @@
         <v>0.4905263157894737</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>107</v>
       </c>
@@ -5388,7 +5391,7 @@
         <v>0.48842105263157892</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>107</v>
       </c>
@@ -5408,7 +5411,7 @@
         <v>0.4863157894736842</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>107</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>0.48421052631578948</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>107</v>
       </c>
@@ -5448,7 +5451,7 @@
         <v>0.48210526315789476</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>107</v>
       </c>
@@ -5468,7 +5471,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>108</v>
       </c>
@@ -5488,7 +5491,7 @@
         <v>0.47789473684210526</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>108</v>
       </c>
@@ -5508,7 +5511,7 @@
         <v>0.47578947368421054</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>108</v>
       </c>
@@ -5528,7 +5531,7 @@
         <v>0.47368421052631576</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>108</v>
       </c>
@@ -5548,7 +5551,7 @@
         <v>0.47157894736842104</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>108</v>
       </c>
@@ -5568,7 +5571,7 @@
         <v>0.46947368421052632</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>108</v>
       </c>
@@ -5588,7 +5591,7 @@
         <v>0.4673684210526316</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>120</v>
       </c>
@@ -5608,7 +5611,7 @@
         <v>0.46526315789473682</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>120</v>
       </c>
@@ -5628,7 +5631,7 @@
         <v>0.4631578947368421</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>120</v>
       </c>
@@ -5648,7 +5651,7 @@
         <v>0.46105263157894738</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>120</v>
       </c>
@@ -5668,7 +5671,7 @@
         <v>0.4589473684210526</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>120</v>
       </c>
@@ -5688,7 +5691,7 @@
         <v>0.45684210526315788</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>121</v>
       </c>
@@ -5708,7 +5711,7 @@
         <v>0.45473684210526316</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>122</v>
       </c>
@@ -5728,7 +5731,7 @@
         <v>0.45263157894736844</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>122</v>
       </c>
@@ -5748,7 +5751,7 @@
         <v>0.45052631578947366</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>122</v>
       </c>
@@ -5768,7 +5771,7 @@
         <v>0.44842105263157894</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>122</v>
       </c>
@@ -5788,7 +5791,7 @@
         <v>0.44631578947368422</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>122</v>
       </c>
@@ -5808,7 +5811,7 @@
         <v>0.4442105263157895</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>122</v>
       </c>
@@ -5828,7 +5831,7 @@
         <v>0.44210526315789472</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>122</v>
       </c>
@@ -5848,7 +5851,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>122</v>
       </c>
@@ -5868,7 +5871,7 @@
         <v>0.43789473684210528</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>122</v>
       </c>
@@ -5888,7 +5891,7 @@
         <v>0.4357894736842105</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>122</v>
       </c>
@@ -5908,7 +5911,7 @@
         <v>0.43368421052631578</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>122</v>
       </c>
@@ -5928,7 +5931,7 @@
         <v>0.43157894736842106</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>122</v>
       </c>
@@ -5948,7 +5951,7 @@
         <v>0.42947368421052634</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>122</v>
       </c>
@@ -5968,7 +5971,7 @@
         <v>0.42736842105263156</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>122</v>
       </c>
@@ -5988,7 +5991,7 @@
         <v>0.42526315789473684</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>122</v>
       </c>
@@ -6008,7 +6011,7 @@
         <v>0.42315789473684212</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>122</v>
       </c>
@@ -6028,7 +6031,7 @@
         <v>0.42105263157894735</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>122</v>
       </c>
@@ -6048,7 +6051,7 @@
         <v>0.41894736842105262</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>122</v>
       </c>
@@ -6068,7 +6071,7 @@
         <v>0.4168421052631579</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>122</v>
       </c>
@@ -6088,7 +6091,7 @@
         <v>0.41473684210526318</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>122</v>
       </c>
@@ -6108,7 +6111,7 @@
         <v>0.4126315789473684</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>123</v>
       </c>
@@ -6128,7 +6131,7 @@
         <v>0.41052631578947368</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>123</v>
       </c>
@@ -6148,7 +6151,7 @@
         <v>0.40842105263157896</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>123</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>0.40631578947368419</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>123</v>
       </c>
@@ -6188,7 +6191,7 @@
         <v>0.40421052631578946</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>123</v>
       </c>
@@ -6208,7 +6211,7 @@
         <v>0.40210526315789474</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>123</v>
       </c>
@@ -6228,7 +6231,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>135</v>
       </c>
@@ -6248,7 +6251,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>135</v>
       </c>
@@ -6268,7 +6271,7 @@
         <v>0.39578947368421052</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>135</v>
       </c>
@@ -6288,7 +6291,7 @@
         <v>0.3936842105263158</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>135</v>
       </c>
@@ -6308,7 +6311,7 @@
         <v>0.39157894736842103</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>135</v>
       </c>
@@ -6328,7 +6331,7 @@
         <v>0.38947368421052631</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>135</v>
       </c>
@@ -6348,7 +6351,7 @@
         <v>0.38736842105263158</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>136</v>
       </c>
@@ -6368,7 +6371,7 @@
         <v>0.38526315789473686</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>136</v>
       </c>
@@ -6388,7 +6391,7 @@
         <v>0.38315789473684209</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>136</v>
       </c>
@@ -6408,7 +6411,7 @@
         <v>0.38105263157894737</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>136</v>
       </c>
@@ -6428,7 +6431,7 @@
         <v>0.37894736842105264</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>136</v>
       </c>
@@ -6448,7 +6451,7 @@
         <v>0.37684210526315787</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>136</v>
       </c>
@@ -6468,7 +6471,7 @@
         <v>0.37473684210526315</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>136</v>
       </c>
@@ -6488,7 +6491,7 @@
         <v>0.37263157894736842</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>137</v>
       </c>
@@ -6508,7 +6511,7 @@
         <v>0.3705263157894737</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>137</v>
       </c>
@@ -6528,7 +6531,7 @@
         <v>0.36842105263157893</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>137</v>
       </c>
@@ -6548,7 +6551,7 @@
         <v>0.36631578947368421</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>137</v>
       </c>
@@ -6568,7 +6571,7 @@
         <v>0.36421052631578948</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>137</v>
       </c>
@@ -6588,7 +6591,7 @@
         <v>0.36210526315789476</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>137</v>
       </c>
@@ -6608,7 +6611,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>137</v>
       </c>
@@ -6628,7 +6631,7 @@
         <v>0.35789473684210527</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>137</v>
       </c>
@@ -6648,7 +6651,7 @@
         <v>0.35578947368421054</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>137</v>
       </c>
@@ -6668,7 +6671,7 @@
         <v>0.35368421052631577</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>137</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>0.35157894736842105</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>137</v>
       </c>
@@ -6708,7 +6711,7 @@
         <v>0.34947368421052633</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>137</v>
       </c>
@@ -6728,7 +6731,7 @@
         <v>0.3473684210526316</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>137</v>
       </c>
@@ -6748,7 +6751,7 @@
         <v>0.34526315789473683</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>137</v>
       </c>
@@ -6768,7 +6771,7 @@
         <v>0.34315789473684211</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>137</v>
       </c>
@@ -6788,7 +6791,7 @@
         <v>0.34105263157894739</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>137</v>
       </c>
@@ -6808,7 +6811,7 @@
         <v>0.33894736842105261</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>137</v>
       </c>
@@ -6828,7 +6831,7 @@
         <v>0.33684210526315789</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>137</v>
       </c>
@@ -6848,7 +6851,7 @@
         <v>0.33473684210526317</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>137</v>
       </c>
@@ -6868,7 +6871,7 @@
         <v>0.33263157894736844</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>137</v>
       </c>
@@ -6888,7 +6891,7 @@
         <v>0.33052631578947367</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>137</v>
       </c>
@@ -6908,7 +6911,7 @@
         <v>0.32842105263157895</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>138</v>
       </c>
@@ -6928,7 +6931,7 @@
         <v>0.32631578947368423</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>138</v>
       </c>
@@ -6948,7 +6951,7 @@
         <v>0.32421052631578945</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>138</v>
       </c>
@@ -6968,7 +6971,7 @@
         <v>0.32210526315789473</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>138</v>
       </c>
@@ -6988,7 +6991,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>138</v>
       </c>
@@ -7008,7 +7011,7 @@
         <v>0.31789473684210529</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>138</v>
       </c>
@@ -7028,7 +7031,7 @@
         <v>0.31578947368421051</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>138</v>
       </c>
@@ -7048,7 +7051,7 @@
         <v>0.31368421052631579</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>150</v>
       </c>
@@ -7068,7 +7071,7 @@
         <v>0.31157894736842107</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>151</v>
       </c>
@@ -7088,7 +7091,7 @@
         <v>0.30947368421052629</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>152</v>
       </c>
@@ -7108,7 +7111,7 @@
         <v>0.30736842105263157</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>152</v>
       </c>
@@ -7128,7 +7131,7 @@
         <v>0.30526315789473685</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>152</v>
       </c>
@@ -7148,7 +7151,7 @@
         <v>0.30315789473684213</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>152</v>
       </c>
@@ -7168,7 +7171,7 @@
         <v>0.30105263157894735</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>152</v>
       </c>
@@ -7188,7 +7191,7 @@
         <v>0.29894736842105263</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>152</v>
       </c>
@@ -7208,7 +7211,7 @@
         <v>0.29684210526315791</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>152</v>
       </c>
@@ -7228,7 +7231,7 @@
         <v>0.29473684210526313</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>152</v>
       </c>
@@ -7248,7 +7251,7 @@
         <v>0.29263157894736841</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>152</v>
       </c>
@@ -7268,7 +7271,7 @@
         <v>0.29052631578947369</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>152</v>
       </c>
@@ -7288,7 +7291,7 @@
         <v>0.28842105263157897</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>152</v>
       </c>
@@ -7308,7 +7311,7 @@
         <v>0.28631578947368419</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>153</v>
       </c>
@@ -7328,7 +7331,7 @@
         <v>0.28421052631578947</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>153</v>
       </c>
@@ -7348,7 +7351,7 @@
         <v>0.28210526315789475</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>153</v>
       </c>
@@ -7368,7 +7371,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>153</v>
       </c>
@@ -7388,7 +7391,7 @@
         <v>0.27789473684210525</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>153</v>
       </c>
@@ -7408,7 +7411,7 @@
         <v>0.27578947368421053</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>153</v>
       </c>
@@ -7428,7 +7431,7 @@
         <v>0.27368421052631581</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>153</v>
       </c>
@@ -7448,7 +7451,7 @@
         <v>0.27157894736842103</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>153</v>
       </c>
@@ -7468,7 +7471,7 @@
         <v>0.26947368421052631</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>153</v>
       </c>
@@ -7488,7 +7491,7 @@
         <v>0.26736842105263159</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>153</v>
       </c>
@@ -7508,7 +7511,7 @@
         <v>0.26526315789473687</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>166</v>
       </c>
@@ -7528,7 +7531,7 @@
         <v>0.26315789473684209</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>166</v>
       </c>
@@ -7548,7 +7551,7 @@
         <v>0.26105263157894737</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>167</v>
       </c>
@@ -7568,7 +7571,7 @@
         <v>0.25894736842105265</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>167</v>
       </c>
@@ -7588,7 +7591,7 @@
         <v>0.25684210526315787</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>167</v>
       </c>
@@ -7608,7 +7611,7 @@
         <v>0.25473684210526315</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>168</v>
       </c>
@@ -7628,7 +7631,7 @@
         <v>0.25263157894736843</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>168</v>
       </c>
@@ -7648,7 +7651,7 @@
         <v>0.25052631578947371</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>168</v>
       </c>
@@ -7668,7 +7671,7 @@
         <v>0.24842105263157896</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>168</v>
       </c>
@@ -7688,7 +7691,7 @@
         <v>0.24631578947368421</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>180</v>
       </c>
@@ -7708,7 +7711,7 @@
         <v>0.24421052631578946</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>182</v>
       </c>
@@ -7728,7 +7731,7 @@
         <v>0.24210526315789474</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>182</v>
       </c>
@@ -7748,7 +7751,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>182</v>
       </c>
@@ -7768,7 +7771,7 @@
         <v>0.23789473684210527</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>183</v>
       </c>
@@ -7788,7 +7791,7 @@
         <v>0.23578947368421052</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>183</v>
       </c>
@@ -7808,7 +7811,7 @@
         <v>0.2336842105263158</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>183</v>
       </c>
@@ -7828,7 +7831,7 @@
         <v>0.23157894736842105</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>183</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>0.2294736842105263</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>196</v>
       </c>
@@ -7868,7 +7871,7 @@
         <v>0.22736842105263158</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>212</v>
       </c>
@@ -7888,7 +7891,7 @@
         <v>0.22526315789473683</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>212</v>
       </c>
@@ -7908,7 +7911,7 @@
         <v>0.22315789473684211</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>213</v>
       </c>
@@ -7928,7 +7931,7 @@
         <v>0.22105263157894736</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>225</v>
       </c>
@@ -7948,7 +7951,7 @@
         <v>0.21894736842105264</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>226</v>
       </c>
@@ -7968,7 +7971,7 @@
         <v>0.21684210526315789</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>227</v>
       </c>
@@ -7988,7 +7991,7 @@
         <v>0.21473684210526317</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>227</v>
       </c>
@@ -8008,7 +8011,7 @@
         <v>0.21263157894736842</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>227</v>
       </c>
@@ -8028,7 +8031,7 @@
         <v>0.21052631578947367</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>228</v>
       </c>
@@ -8048,7 +8051,7 @@
         <v>0.20842105263157895</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>228</v>
       </c>
@@ -8068,7 +8071,7 @@
         <v>0.2063157894736842</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>256</v>
       </c>
@@ -8088,7 +8091,7 @@
         <v>0.20421052631578948</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>287</v>
       </c>
@@ -8108,7 +8111,7 @@
         <v>0.20210526315789473</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>362</v>
       </c>
@@ -8128,7 +8131,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>436</v>
       </c>
@@ -8148,7 +8151,7 @@
         <v>0.19789473684210526</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C387">
         <v>128</v>
       </c>
@@ -8162,7 +8165,7 @@
         <v>0.19578947368421051</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C388">
         <v>128</v>
       </c>
@@ -8176,7 +8179,7 @@
         <v>0.19368421052631579</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C389">
         <v>128</v>
       </c>
@@ -8190,7 +8193,7 @@
         <v>0.19157894736842104</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C390">
         <v>128</v>
       </c>
@@ -8204,7 +8207,7 @@
         <v>0.18947368421052632</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C391">
         <v>129</v>
       </c>
@@ -8218,7 +8221,7 @@
         <v>0.18736842105263157</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C392">
         <v>129</v>
       </c>
@@ -8232,7 +8235,7 @@
         <v>0.18526315789473685</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C393">
         <v>129</v>
       </c>
@@ -8246,7 +8249,7 @@
         <v>0.1831578947368421</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C394">
         <v>129</v>
       </c>
@@ -8260,7 +8263,7 @@
         <v>0.18105263157894738</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C395">
         <v>129</v>
       </c>
@@ -8274,7 +8277,7 @@
         <v>0.17894736842105263</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C396">
         <v>129</v>
       </c>
@@ -8288,7 +8291,7 @@
         <v>0.17684210526315788</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C397">
         <v>129</v>
       </c>
@@ -8302,7 +8305,7 @@
         <v>0.17473684210526316</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C398">
         <v>130</v>
       </c>
@@ -8316,7 +8319,7 @@
         <v>0.17263157894736841</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C399">
         <v>130</v>
       </c>
@@ -8330,7 +8333,7 @@
         <v>0.17052631578947369</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C400">
         <v>130</v>
       </c>
@@ -8344,7 +8347,7 @@
         <v>0.16842105263157894</v>
       </c>
     </row>
-    <row r="401" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C401">
         <v>130</v>
       </c>
@@ -8358,7 +8361,7 @@
         <v>0.16631578947368422</v>
       </c>
     </row>
-    <row r="402" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C402">
         <v>130</v>
       </c>
@@ -8372,7 +8375,7 @@
         <v>0.16421052631578947</v>
       </c>
     </row>
-    <row r="403" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C403">
         <v>130</v>
       </c>
@@ -8386,7 +8389,7 @@
         <v>0.16210526315789472</v>
       </c>
     </row>
-    <row r="404" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="404" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C404">
         <v>130</v>
       </c>
@@ -8400,7 +8403,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="405" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C405">
         <v>131</v>
       </c>
@@ -8414,7 +8417,7 @@
         <v>0.15789473684210525</v>
       </c>
     </row>
-    <row r="406" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C406">
         <v>131</v>
       </c>
@@ -8428,7 +8431,7 @@
         <v>0.15578947368421053</v>
       </c>
     </row>
-    <row r="407" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C407">
         <v>131</v>
       </c>
@@ -8442,7 +8445,7 @@
         <v>0.15368421052631578</v>
       </c>
     </row>
-    <row r="408" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C408">
         <v>131</v>
       </c>
@@ -8456,7 +8459,7 @@
         <v>0.15157894736842106</v>
       </c>
     </row>
-    <row r="409" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C409">
         <v>131</v>
       </c>
@@ -8470,7 +8473,7 @@
         <v>0.14947368421052631</v>
       </c>
     </row>
-    <row r="410" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C410">
         <v>131</v>
       </c>
@@ -8484,7 +8487,7 @@
         <v>0.14736842105263157</v>
       </c>
     </row>
-    <row r="411" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C411">
         <v>131</v>
       </c>
@@ -8498,7 +8501,7 @@
         <v>0.14526315789473684</v>
       </c>
     </row>
-    <row r="412" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C412">
         <v>131</v>
       </c>
@@ -8512,7 +8515,7 @@
         <v>0.1431578947368421</v>
       </c>
     </row>
-    <row r="413" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C413">
         <v>131</v>
       </c>
@@ -8526,7 +8529,7 @@
         <v>0.14105263157894737</v>
       </c>
     </row>
-    <row r="414" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C414">
         <v>131</v>
       </c>
@@ -8540,7 +8543,7 @@
         <v>0.13894736842105262</v>
       </c>
     </row>
-    <row r="415" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C415">
         <v>131</v>
       </c>
@@ -8554,7 +8557,7 @@
         <v>0.1368421052631579</v>
       </c>
     </row>
-    <row r="416" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C416">
         <v>143</v>
       </c>
@@ -8568,7 +8571,7 @@
         <v>0.13473684210526315</v>
       </c>
     </row>
-    <row r="417" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C417">
         <v>143</v>
       </c>
@@ -8582,7 +8585,7 @@
         <v>0.13263157894736843</v>
       </c>
     </row>
-    <row r="418" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C418">
         <v>143</v>
       </c>
@@ -8596,7 +8599,7 @@
         <v>0.13052631578947368</v>
       </c>
     </row>
-    <row r="419" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C419">
         <v>143</v>
       </c>
@@ -8610,7 +8613,7 @@
         <v>0.12842105263157894</v>
       </c>
     </row>
-    <row r="420" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C420">
         <v>143</v>
       </c>
@@ -8624,7 +8627,7 @@
         <v>0.12631578947368421</v>
       </c>
     </row>
-    <row r="421" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C421">
         <v>143</v>
       </c>
@@ -8638,7 +8641,7 @@
         <v>0.12421052631578948</v>
       </c>
     </row>
-    <row r="422" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C422">
         <v>143</v>
       </c>
@@ -8652,7 +8655,7 @@
         <v>0.12210526315789473</v>
       </c>
     </row>
-    <row r="423" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C423">
         <v>143</v>
       </c>
@@ -8666,7 +8669,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="424" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C424">
         <v>143</v>
       </c>
@@ -8680,7 +8683,7 @@
         <v>0.11789473684210526</v>
       </c>
     </row>
-    <row r="425" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C425">
         <v>143</v>
       </c>
@@ -8694,7 +8697,7 @@
         <v>0.11578947368421053</v>
       </c>
     </row>
-    <row r="426" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C426">
         <v>143</v>
       </c>
@@ -8708,7 +8711,7 @@
         <v>0.11368421052631579</v>
       </c>
     </row>
-    <row r="427" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C427">
         <v>143</v>
       </c>
@@ -8722,7 +8725,7 @@
         <v>0.11157894736842106</v>
       </c>
     </row>
-    <row r="428" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C428">
         <v>143</v>
       </c>
@@ -8736,7 +8739,7 @@
         <v>0.10947368421052632</v>
       </c>
     </row>
-    <row r="429" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C429">
         <v>143</v>
       </c>
@@ -8750,7 +8753,7 @@
         <v>0.10736842105263159</v>
       </c>
     </row>
-    <row r="430" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C430">
         <v>143</v>
       </c>
@@ -8764,7 +8767,7 @@
         <v>0.10526315789473684</v>
       </c>
     </row>
-    <row r="431" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C431">
         <v>143</v>
       </c>
@@ -8778,7 +8781,7 @@
         <v>0.1031578947368421</v>
       </c>
     </row>
-    <row r="432" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C432">
         <v>143</v>
       </c>
@@ -8792,7 +8795,7 @@
         <v>0.10105263157894737</v>
       </c>
     </row>
-    <row r="433" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="433" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C433">
         <v>143</v>
       </c>
@@ -8806,7 +8809,7 @@
         <v>9.8947368421052631E-2</v>
       </c>
     </row>
-    <row r="434" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="434" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C434">
         <v>143</v>
       </c>
@@ -8820,7 +8823,7 @@
         <v>9.6842105263157896E-2</v>
       </c>
     </row>
-    <row r="435" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="435" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C435">
         <v>144</v>
       </c>
@@ -8834,7 +8837,7 @@
         <v>9.4736842105263161E-2</v>
       </c>
     </row>
-    <row r="436" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="436" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C436">
         <v>145</v>
       </c>
@@ -8848,7 +8851,7 @@
         <v>9.2631578947368426E-2</v>
       </c>
     </row>
-    <row r="437" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="437" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C437">
         <v>145</v>
       </c>
@@ -8862,7 +8865,7 @@
         <v>9.0526315789473691E-2</v>
       </c>
     </row>
-    <row r="438" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="438" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C438">
         <v>145</v>
       </c>
@@ -8876,7 +8879,7 @@
         <v>8.8421052631578942E-2</v>
       </c>
     </row>
-    <row r="439" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="439" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C439">
         <v>146</v>
       </c>
@@ -8890,7 +8893,7 @@
         <v>8.6315789473684207E-2</v>
       </c>
     </row>
-    <row r="440" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="440" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C440">
         <v>146</v>
       </c>
@@ -8904,7 +8907,7 @@
         <v>8.4210526315789472E-2</v>
       </c>
     </row>
-    <row r="441" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="441" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C441">
         <v>158</v>
       </c>
@@ -8918,7 +8921,7 @@
         <v>8.2105263157894737E-2</v>
       </c>
     </row>
-    <row r="442" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="442" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C442">
         <v>158</v>
       </c>
@@ -8932,7 +8935,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="443" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="443" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C443">
         <v>158</v>
       </c>
@@ -8946,7 +8949,7 @@
         <v>7.7894736842105267E-2</v>
       </c>
     </row>
-    <row r="444" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="444" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C444">
         <v>158</v>
       </c>
@@ -8960,7 +8963,7 @@
         <v>7.5789473684210532E-2</v>
       </c>
     </row>
-    <row r="445" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="445" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C445">
         <v>158</v>
       </c>
@@ -8974,7 +8977,7 @@
         <v>7.3684210526315783E-2</v>
       </c>
     </row>
-    <row r="446" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="446" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C446">
         <v>158</v>
       </c>
@@ -8988,7 +8991,7 @@
         <v>7.1578947368421048E-2</v>
       </c>
     </row>
-    <row r="447" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="447" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C447">
         <v>158</v>
       </c>
@@ -9002,7 +9005,7 @@
         <v>6.9473684210526312E-2</v>
       </c>
     </row>
-    <row r="448" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="448" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C448">
         <v>158</v>
       </c>
@@ -9016,7 +9019,7 @@
         <v>6.7368421052631577E-2</v>
       </c>
     </row>
-    <row r="449" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="449" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C449">
         <v>158</v>
       </c>
@@ -9030,7 +9033,7 @@
         <v>6.5263157894736842E-2</v>
       </c>
     </row>
-    <row r="450" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="450" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C450">
         <v>158</v>
       </c>
@@ -9044,7 +9047,7 @@
         <v>6.3157894736842107E-2</v>
       </c>
     </row>
-    <row r="451" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="451" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C451">
         <v>158</v>
       </c>
@@ -9058,7 +9061,7 @@
         <v>6.1052631578947365E-2</v>
       </c>
     </row>
-    <row r="452" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="452" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C452">
         <v>160</v>
       </c>
@@ -9072,7 +9075,7 @@
         <v>5.894736842105263E-2</v>
       </c>
     </row>
-    <row r="453" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="453" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C453">
         <v>161</v>
       </c>
@@ -9086,7 +9089,7 @@
         <v>5.6842105263157895E-2</v>
       </c>
     </row>
-    <row r="454" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="454" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C454">
         <v>161</v>
       </c>
@@ -9100,7 +9103,7 @@
         <v>5.473684210526316E-2</v>
       </c>
     </row>
-    <row r="455" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="455" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C455">
         <v>173</v>
       </c>
@@ -9114,7 +9117,7 @@
         <v>5.2631578947368418E-2</v>
       </c>
     </row>
-    <row r="456" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="456" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C456">
         <v>173</v>
       </c>
@@ -9128,7 +9131,7 @@
         <v>5.0526315789473683E-2</v>
       </c>
     </row>
-    <row r="457" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="457" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C457">
         <v>173</v>
       </c>
@@ -9142,7 +9145,7 @@
         <v>4.8421052631578948E-2</v>
       </c>
     </row>
-    <row r="458" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="458" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C458">
         <v>173</v>
       </c>
@@ -9156,7 +9159,7 @@
         <v>4.6315789473684213E-2</v>
       </c>
     </row>
-    <row r="459" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="459" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C459">
         <v>173</v>
       </c>
@@ -9170,7 +9173,7 @@
         <v>4.4210526315789471E-2</v>
       </c>
     </row>
-    <row r="460" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="460" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C460">
         <v>173</v>
       </c>
@@ -9184,7 +9187,7 @@
         <v>4.2105263157894736E-2</v>
       </c>
     </row>
-    <row r="461" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="461" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C461">
         <v>173</v>
       </c>
@@ -9198,7 +9201,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="462" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="462" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C462">
         <v>173</v>
       </c>
@@ -9212,7 +9215,7 @@
         <v>3.7894736842105266E-2</v>
       </c>
     </row>
-    <row r="463" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="463" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C463">
         <v>174</v>
       </c>
@@ -9226,7 +9229,7 @@
         <v>3.5789473684210524E-2</v>
       </c>
     </row>
-    <row r="464" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="464" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C464">
         <v>176</v>
       </c>
@@ -9240,7 +9243,7 @@
         <v>3.3684210526315789E-2</v>
       </c>
     </row>
-    <row r="465" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="465" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C465">
         <v>176</v>
       </c>
@@ -9254,7 +9257,7 @@
         <v>3.1578947368421054E-2</v>
       </c>
     </row>
-    <row r="466" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="466" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C466">
         <v>176</v>
       </c>
@@ -9268,7 +9271,7 @@
         <v>2.9473684210526315E-2</v>
       </c>
     </row>
-    <row r="467" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="467" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C467">
         <v>188</v>
       </c>
@@ -9282,7 +9285,7 @@
         <v>2.736842105263158E-2</v>
       </c>
     </row>
-    <row r="468" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="468" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C468">
         <v>188</v>
       </c>
@@ -9296,7 +9299,7 @@
         <v>2.5263157894736842E-2</v>
       </c>
     </row>
-    <row r="469" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="469" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C469">
         <v>188</v>
       </c>
@@ -9310,7 +9313,7 @@
         <v>2.3157894736842106E-2</v>
       </c>
     </row>
-    <row r="470" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="470" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C470">
         <v>188</v>
       </c>
@@ -9324,7 +9327,7 @@
         <v>2.1052631578947368E-2</v>
       </c>
     </row>
-    <row r="471" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="471" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C471">
         <v>188</v>
       </c>
@@ -9338,7 +9341,7 @@
         <v>1.8947368421052633E-2</v>
       </c>
     </row>
-    <row r="472" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="472" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C472">
         <v>190</v>
       </c>
@@ -9352,7 +9355,7 @@
         <v>1.6842105263157894E-2</v>
       </c>
     </row>
-    <row r="473" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="473" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C473">
         <v>204</v>
       </c>
@@ -9366,7 +9369,7 @@
         <v>1.4736842105263158E-2</v>
       </c>
     </row>
-    <row r="474" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="474" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C474">
         <v>218</v>
       </c>
@@ -9380,7 +9383,7 @@
         <v>1.2631578947368421E-2</v>
       </c>
     </row>
-    <row r="475" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="475" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C475">
         <v>218</v>
       </c>
@@ -9394,7 +9397,7 @@
         <v>1.0526315789473684E-2</v>
       </c>
     </row>
-    <row r="476" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="476" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C476">
         <v>221</v>
       </c>
@@ -9408,7 +9411,7 @@
         <v>8.4210526315789472E-3</v>
       </c>
     </row>
-    <row r="477" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="477" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C477">
         <v>221</v>
       </c>
@@ -9422,7 +9425,7 @@
         <v>6.3157894736842104E-3</v>
       </c>
     </row>
-    <row r="478" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="478" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C478">
         <v>233</v>
       </c>
@@ -9436,7 +9439,7 @@
         <v>4.2105263157894736E-3</v>
       </c>
     </row>
-    <row r="479" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="479" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C479">
         <v>236</v>
       </c>
@@ -9450,7 +9453,7 @@
         <v>2.1052631578947368E-3</v>
       </c>
     </row>
-    <row r="480" spans="3:6" x14ac:dyDescent="0.2">
+    <row r="480" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C480">
         <v>236</v>
       </c>
@@ -9458,7 +9461,7 @@
         <v>1.2474012474012475E-2</v>
       </c>
     </row>
-    <row r="481" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="481" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C481">
         <v>248</v>
       </c>
@@ -9466,7 +9469,7 @@
         <v>1.0395010395010396E-2</v>
       </c>
     </row>
-    <row r="482" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="482" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C482">
         <v>267</v>
       </c>
@@ -9474,7 +9477,7 @@
         <v>8.3160083160083165E-3</v>
       </c>
     </row>
-    <row r="483" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="483" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C483">
         <v>293</v>
       </c>
@@ -9482,7 +9485,7 @@
         <v>6.2370062370062374E-3</v>
       </c>
     </row>
-    <row r="484" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="484" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C484">
         <v>323</v>
       </c>
@@ -9490,7 +9493,7 @@
         <v>4.1580041580041582E-3</v>
       </c>
     </row>
-    <row r="485" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="485" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C485">
         <v>459</v>
       </c>
